--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/ruimtelijkeplannen/ruimtelijkeplannen.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/ruimtelijkeplannen/ruimtelijkeplannen.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:K20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,88 +407,701 @@
         <v>_type</v>
       </c>
       <c r="C1" t="str">
+        <v>altLabel</v>
+      </c>
+      <c r="D1" t="str">
         <v>definition</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>inScheme</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>code</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>note</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>prefLabel</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>topConceptOf</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
+        <v>scopeNote</v>
+      </c>
+      <c r="K1" t="str">
         <v>hasTopConcept</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/voorbeeld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/bevat-planologische-compensatie</v>
       </c>
       <c r="B2" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C2" t="str">
-        <v>TODO: voorbeeldconcept; vervang door de eigenlijke concepten.</v>
+        <v>Bevat planologische compensatie</v>
       </c>
       <c r="D2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen</v>
+        <v>Deze procedure genereert een positieve balans.</v>
       </c>
       <c r="E2" t="str">
-        <v>voorbeeld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
       </c>
       <c r="F2" t="str">
-        <v>TODO: voorbeeldconcept; vervang door de eigenlijke concepten.</v>
+        <v>BEVAT_PLANOLOGISCHE_COMPENSATIE</v>
       </c>
       <c r="G2" t="str">
-        <v>voorbeeldconcept</v>
+        <v>Deze procedure genereert een positieve balans.</v>
       </c>
       <c r="H2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen</v>
+        <v>Het plan bevat compensatie</v>
       </c>
       <c r="I2" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J2" t="str">
+        <v>null</v>
+      </c>
+      <c r="K2" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/delegatie</v>
+      </c>
+      <c r="B3" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C3" t="str">
+        <v>null</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Via een delegatie draagt een plannende overheid de bevoegdheid om een planproces te voeren over aan een andere (hogere of lagere) plannende overheid.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F3" t="str">
+        <v>DELEGATIE</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Via een delegatie draagt een plannende overheid de bevoegdheid om een planproces te voeren over aan een andere (hogere of lagere) plannende overheid.</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Delegatie</v>
+      </c>
+      <c r="I3" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J3" t="str">
+        <v>null</v>
+      </c>
+      <c r="K3" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/gebruikersschade</v>
+      </c>
+      <c r="B4" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C4" t="str">
+        <v>null</v>
+      </c>
+      <c r="D4" t="str">
+        <v>De schade die een landbouwer lijdt wanneer de landbouwgrond aan gebruiksbeperkingen moet voldoen.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F4" t="str">
+        <v>GEBRUIKERSSCHADE</v>
+      </c>
+      <c r="G4" t="str">
+        <v>De schade die een landbouwer lijdt wanneer de landbouwgrond aan gebruiksbeperkingen moet voldoen.|Bijvoorbeeld een bestemmingswijziging (van landbouw naar natuur of bos), het opleggen van een erfdienstbaarheid of een overdruk in een ruimtelijk plan.</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Gebruikersschade</v>
+      </c>
+      <c r="I4" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Bijvoorbeeld een bestemmingswijziging (van landbouw naar natuur of bos), het opleggen van een erfdienstbaarheid of een overdruk in een ruimtelijk plan.</v>
+      </c>
+      <c r="K4" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/grensoverschrijdende-effecten</v>
+      </c>
+      <c r="B5" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C5" t="str">
+        <v>null</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Mogelijke effecten in grensgemeenten waarvoor grensoverschrijdende instanties geraadpleegd moeten worden en/of in het planproces betrokken worden.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F5" t="str">
+        <v>GRENSOVERSCHRIJDENDE_EFFECTEN</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Mogelijke effecten in grensgemeenten waarvoor grensoverschrijdende instanties geraadpleegd moeten worden en/of in het planproces betrokken worden.</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Grensoverschrijdende effecten</v>
+      </c>
+      <c r="I5" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J5" t="str">
+        <v>null</v>
+      </c>
+      <c r="K5" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/herneming</v>
+      </c>
+      <c r="B6" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C6" t="str">
+        <v>null</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Wanneer een RvS-procedure een plan geheel of gedeeltelijk vernietigt, kan de initiatiefnemer beslissen om het plan geheel of gedeeltelijk te hernemen.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F6" t="str">
+        <v>HERNEMING</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Wanneer een RvS-procedure een plan geheel of gedeeltelijk vernietigt, kan de initiatiefnemer beslissen om het plan geheel of gedeeltelijk te hernemen.</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Herneming</v>
+      </c>
+      <c r="I6" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J6" t="str">
+        <v>null</v>
+      </c>
+      <c r="K6" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/kapitaalschade</v>
+      </c>
+      <c r="B7" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C7" t="str">
+        <v>null</v>
+      </c>
+      <c r="D7" t="str">
+        <v>De schade die de eigenaar van landbouwgrond lijdt doordat de overheid de economische mogelijkheden van die grond beperkt.</v>
+      </c>
+      <c r="E7" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F7" t="str">
+        <v>KAPITAALSCHADE</v>
+      </c>
+      <c r="G7" t="str">
+        <v>De schade die de eigenaar van landbouwgrond lijdt doordat de overheid de economische mogelijkheden van die grond beperkt.</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Kapitaalschade</v>
+      </c>
+      <c r="I7" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J7" t="str">
+        <v>null</v>
+      </c>
+      <c r="K7" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/onteigening</v>
+      </c>
+      <c r="B8" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C8" t="str">
+        <v>null</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Instrument om het gebruik van gronden te regelen.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F8" t="str">
+        <v>ONTEIGENING</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Instrument om het gebruik van gronden te regelen.|De noodzaak en proportionaliteit van de onteigening moeten goed gemotiveerd worden, inclusief bewijs dat alternatieven niet haalbaar zijn.</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Onteigening</v>
+      </c>
+      <c r="I8" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J8" t="str">
+        <v>De noodzaak en proportionaliteit van de onteigening moeten goed gemotiveerd worden, inclusief bewijs dat alternatieven niet haalbaar zijn.</v>
+      </c>
+      <c r="K8" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/overeenkomst</v>
+      </c>
+      <c r="B9" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C9" t="str">
+        <v>null</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Een overeenkomst wordt gemaakt met minstens één andere partij en wordt ten laatste in de fase voorlopige vaststelling opgenomen en mee ter inzage gelegd tijdens het openbaar onderzoek.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F9" t="str">
+        <v>OVEREENKOMST</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Een overeenkomst wordt gemaakt met minstens één andere partij en wordt ten laatste in de fase voorlopige vaststelling opgenomen en mee ter inzage gelegd tijdens het openbaar onderzoek.</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Overeenkomst</v>
+      </c>
+      <c r="I9" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J9" t="str">
+        <v>null</v>
+      </c>
+      <c r="K9" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/passende-beoordeling</v>
+      </c>
+      <c r="B10" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C10" t="str">
+        <v>null</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Een ecologisch onderzoeksrapport dat nagaat of een gepland project negatieve gevolgen heeft voor de natuurlijke kenmerken en instandhoudingsdoelstellingen van een Europees beschermd Natura 2000-gebied.</v>
+      </c>
+      <c r="E10" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PASSENDE_BEOORDELING</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Een ecologisch onderzoeksrapport dat nagaat of een gepland project negatieve gevolgen heeft voor de natuurlijke kenmerken en instandhoudingsdoelstellingen van een Europees beschermd Natura 2000-gebied.</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Passende beoordeling</v>
+      </c>
+      <c r="I10" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J10" t="str">
+        <v>null</v>
+      </c>
+      <c r="K10" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/planbaten</v>
+      </c>
+      <c r="B11" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C11" t="str">
+        <v>null</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Een waardestijging (meerwaarde) van een perceel grond die ontstaat doordat de overheid de bestemming van dat perceel wijzigt.</v>
+      </c>
+      <c r="E11" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PLANBATEN</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Een waardestijging (meerwaarde) van een perceel grond die ontstaat doordat de overheid de bestemming van dat perceel wijzigt.</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Planbaten</v>
+      </c>
+      <c r="I11" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J11" t="str">
+        <v>null</v>
+      </c>
+      <c r="K11" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/planschade</v>
+      </c>
+      <c r="B12" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C12" t="str">
+        <v>null</v>
+      </c>
+      <c r="D12" t="str">
+        <v>De financiële schade of waardevermindering die een eigenaar lijdt doordat de overheid een bestemmingsplan of ruimtelijk plan wijzigt.</v>
+      </c>
+      <c r="E12" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PLANSCHADE</v>
+      </c>
+      <c r="G12" t="str">
+        <v>De financiële schade of waardevermindering die een eigenaar lijdt doordat de overheid een bestemmingsplan of ruimtelijk plan wijzigt.</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Planschade</v>
+      </c>
+      <c r="I12" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J12" t="str">
+        <v>null</v>
+      </c>
+      <c r="K12" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/recht-van-voorkoop</v>
+      </c>
+      <c r="B13" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C13" t="str">
+        <v>null</v>
+      </c>
+      <c r="D13" t="str">
+        <v>TODO: definitie van recht van voorkoop.</v>
+      </c>
+      <c r="E13" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F13" t="str">
+        <v>RECHT_VAN_VOORKOOP</v>
+      </c>
+      <c r="G13" t="str">
+        <v>TODO: definitie van recht van voorkoop.|Belang kennisgeving eigenaars uiterlijk op de dag van inwerkingtreding van het RUP.</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Recht van voorkoop</v>
+      </c>
+      <c r="I13" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Belang kennisgeving eigenaars uiterlijk op de dag van inwerkingtreding van het RUP.</v>
+      </c>
+      <c r="K13" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/ruimtelijk-veiligheidsrapport</v>
+      </c>
+      <c r="B14" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C14" t="str">
+        <v>RVR</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Een ruimtelijk veiligheidsrapport is vereist.</v>
+      </c>
+      <c r="E14" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F14" t="str">
+        <v>RUIMTELIJK_VEILIGHEIDSRAPPORT</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Een ruimtelijk veiligheidsrapport is vereist.</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Ruimtelijk veiligheidsrapport</v>
+      </c>
+      <c r="I14" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J14" t="str">
+        <v>null</v>
+      </c>
+      <c r="K14" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/vereist-planologische-compensatie</v>
+      </c>
+      <c r="B15" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Vereist planologische compensatie</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Deze procedure genereert een negatieve balans.</v>
+      </c>
+      <c r="E15" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F15" t="str">
+        <v>VEREIST_PLANOLOGISCHE_COMPENSATIE</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Deze procedure genereert een negatieve balans.</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Het plan vereist compensatie</v>
+      </c>
+      <c r="I15" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J15" t="str">
+        <v>null</v>
+      </c>
+      <c r="K15" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/verordening</v>
+      </c>
+      <c r="B16" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C16" t="str">
+        <v>null</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Een verordening bevat aanvullende, meer gedetailleerde of thematische regels.</v>
+      </c>
+      <c r="E16" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F16" t="str">
+        <v>VERORDENING</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Een verordening bevat aanvullende, meer gedetailleerde of thematische regels.|Verordeningen kunnen specifieke bepalingen bevatten zoals toegankelijkheid, milieubescherming, maximaal toegelaten activiteiten en functies. Komt niet veel voor bij gewestelijke RUP's.</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Verordening</v>
+      </c>
+      <c r="I16" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Verordeningen kunnen specifieke bepalingen bevatten zoals toegankelijkheid, milieubescherming, maximaal toegelaten activiteiten en functies. Komt niet veel voor bij gewestelijke RUP's.</v>
+      </c>
+      <c r="K16" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/verscherpte-natuurtoets</v>
+      </c>
+      <c r="B17" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C17" t="str">
+        <v>VEN-toets</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Een verplichte beoordeling die onderzoekt of een vergunningsplichtige activiteit onvermijdbare en onherstelbare schade kan veroorzaken aan de natuurlijke kenmerken van een gebied binnen het Vlaams Ecologisch Netwerk.</v>
+      </c>
+      <c r="E17" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="F17" t="str">
+        <v>VERSCHERPTE_NATUURTOETS</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Een verplichte beoordeling die onderzoekt of een vergunningsplichtige activiteit onvermijdbare en onherstelbare schade kan veroorzaken aan de natuurlijke kenmerken van een gebied binnen het Vlaams Ecologisch Netwerk.</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Verscherpte natuurtoets</v>
+      </c>
+      <c r="I17" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="J17" t="str">
+        <v>null</v>
+      </c>
+      <c r="K17" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/voorbeeld</v>
+      </c>
+      <c r="B18" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C18" t="str">
+        <v>null</v>
+      </c>
+      <c r="D18" t="str">
+        <v>TODO: voorbeeldconcept; vervang door de eigenlijke concepten.</v>
+      </c>
+      <c r="E18" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen</v>
       </c>
-      <c r="B3" t="str">
+      <c r="F18" t="str">
+        <v>voorbeeld</v>
+      </c>
+      <c r="G18" t="str">
+        <v>TODO: voorbeeldconcept; vervang door de eigenlijke concepten.</v>
+      </c>
+      <c r="H18" t="str">
+        <v>voorbeeldconcept</v>
+      </c>
+      <c r="I18" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen</v>
+      </c>
+      <c r="J18" t="str">
+        <v>null</v>
+      </c>
+      <c r="K18" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen</v>
+      </c>
+      <c r="B19" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C19" t="str">
+        <v>null</v>
+      </c>
+      <c r="D19" t="str">
         <v>TODO: definitie van het conceptschema ruimtelijkeplannen.</v>
       </c>
-      <c r="D3" t="str">
-        <v>null</v>
-      </c>
-      <c r="E3" t="str">
-        <v>null</v>
-      </c>
-      <c r="F3" t="str">
+      <c r="E19" t="str">
+        <v>null</v>
+      </c>
+      <c r="F19" t="str">
+        <v>null</v>
+      </c>
+      <c r="G19" t="str">
         <v>TODO: definitie van het conceptschema ruimtelijkeplannen.</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H19" t="str">
         <v>conceptschema ruimtelijkeplannen</v>
       </c>
-      <c r="H3" t="str">
-        <v>null</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="I19" t="str">
+        <v>null</v>
+      </c>
+      <c r="J19" t="str">
+        <v>null</v>
+      </c>
+      <c r="K19" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/voorbeeld</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/ruimtelijkeplannen/procedurekenmerken</v>
+      </c>
+      <c r="B20" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C20" t="str">
+        <v>null</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Kenmerken van de procedure van een ruimtelijk plan.</v>
+      </c>
+      <c r="E20" t="str">
+        <v>null</v>
+      </c>
+      <c r="F20" t="str">
+        <v>null</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Kenmerken van de procedure van een ruimtelijk plan.|Voorheen benoemd als voorkomende gevallen.</v>
+      </c>
+      <c r="H20" t="str">
+        <v>procedurekenmerken</v>
+      </c>
+      <c r="I20" t="str">
+        <v>null</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Voorheen benoemd als voorkomende gevallen.</v>
+      </c>
+      <c r="K20" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/bevat-planologische-compensatie|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/delegatie|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/gebruikersschade|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/grensoverschrijdende-effecten|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/herneming|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/kapitaalschade|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/onteigening|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/overeenkomst|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/passende-beoordeling|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/planbaten|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/planschade|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/recht-van-voorkoop|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/ruimtelijk-veiligheidsrapport|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/vereist-planologische-compensatie|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/verordening|https://data.omgeving.vlaanderen.be/id/concept/ruimtelijkeplannen/procedurekenmerken/verscherpte-natuurtoets</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K20"/>
   </ignoredErrors>
 </worksheet>
 </file>